--- a/SurveyQuestions/csvs/hms_survey.xlsx
+++ b/SurveyQuestions/csvs/hms_survey.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Demographics" sheetId="1" state="visible" r:id="rId3"/>
@@ -765,7 +765,7 @@
     <t xml:space="preserve">1=Yes 2=No 3=Prefer not to say</t>
   </si>
   <si>
-    <t xml:space="preserve">If any of the disabilities above are selected</t>
+    <t xml:space="preserve">Display if any option other than "I do not have a disability" is selected for "Do you have a disability or disabilities from any of the following categories?"</t>
   </si>
   <si>
     <t xml:space="preserve">When were you diagnosed with ADHD ?</t>
@@ -1556,15 +1556,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>

--- a/SurveyQuestions/csvs/hms_survey.xlsx
+++ b/SurveyQuestions/csvs/hms_survey.xlsx
@@ -3428,7 +3428,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>1=YourDost 2=Urgent Care or the Emergency Room 3=Provider in the local community (not on campus) 4=Provider in my hometown 5=Provider affiliated with a telehealth company 6=Others</t>
+          <t>1=YourDost 2=Urgent Care or the Emergency Room 3=Provider in the local community (not on campus) 4=Provider in my hometown 5=Provider affiliated with a telehealth company 6=Other (please specify)</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Display if "1=Attention deficit hyperactivity disorder (ADHD or ADD)" is selected for "Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)"</t>
+          <t>Display if "1=Attention deficit hyperactivity disorder (ADHD or ADD)" is selected for "Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)" or "1=Attention deficit/hyperactivity disorders" is selected for "Do you have a disability or disabilities from any of the following categories?"</t>
         </is>
       </c>
     </row>

--- a/SurveyQuestions/csvs/hms_survey.xlsx
+++ b/SurveyQuestions/csvs/hms_survey.xlsx
@@ -3352,7 +3352,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?” Display if “8=No, none of these” is not selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
     </row>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?” Display if “8=No, none of these” is not selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
     </row>

--- a/SurveyQuestions/csvs/hms_survey.xlsx
+++ b/SurveyQuestions/csvs/hms_survey.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" tabRatio="500" firstSheet="2" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" tabRatio="500" firstSheet="2" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Demographics" sheetId="1" r:id="rId1"/>
@@ -17,15 +17,14 @@
     <sheet name="Mental Health Service Utilizati" sheetId="3" r:id="rId3"/>
     <sheet name="Overall Health" sheetId="4" r:id="rId4"/>
     <sheet name="Academic Persistence, Retention" sheetId="5" r:id="rId5"/>
-    <sheet name="Financial Stress" sheetId="6" r:id="rId6"/>
-    <sheet name="Sheet1" sheetId="7" r:id="rId7"/>
+    <sheet name="Financial Stress" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="474">
   <si>
     <t>Module</t>
   </si>
@@ -1458,7 +1457,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1466,30 +1465,13 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FFE7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FFD9EAF7"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1504,21 +1486,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4658,209 +4628,6 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="27.42578125" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="39.7109375" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:5" ht="102" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-    </row>
-    <row r="14" spans="1:5" ht="180" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AB14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/SurveyQuestions/csvs/hms_survey.xlsx
+++ b/SurveyQuestions/csvs/hms_survey.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" tabRatio="500" firstSheet="2" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" tabRatio="500" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Demographics" sheetId="1" r:id="rId1"/>
@@ -17,14 +17,14 @@
     <sheet name="Mental Health Service Utilizati" sheetId="3" r:id="rId3"/>
     <sheet name="Overall Health" sheetId="4" r:id="rId4"/>
     <sheet name="Academic Persistence, Retention" sheetId="5" r:id="rId5"/>
-    <sheet name="Financial Stress" sheetId="7" r:id="rId6"/>
+    <sheet name="Financial Stress" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="476">
   <si>
     <t>Module</t>
   </si>
@@ -953,7 +953,7 @@
     <t>1=Psychostimulants (methylphenidate (Ritalin, or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Other medication for mental or emotional health (please specify) 8=None of the above [mutually exclusive]</t>
   </si>
   <si>
-    <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?” Display if “8=No, none of these” is not selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+    <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
   </si>
   <si>
     <t>In the past 12 months, have you used your prescription stimulant (e.g., Ritalin, Adderall) in any way not directed by a doctor (e.g., use in greater amounts or more often than directed)?</t>
@@ -1381,6 +1381,9 @@
     <t>Financial Stress</t>
   </si>
   <si>
+    <t>Socioeconom ic status</t>
+  </si>
+  <si>
     <t>Within the past 12 months I worried whether our food would run out before we got money to buy more.</t>
   </si>
   <si>
@@ -1438,7 +1441,7 @@
     <t>Have you ever participated in sports betting?</t>
   </si>
   <si>
-    <t>How often have you used online sportsbook applications (e.g., Dream11,Parimatch,Dafabet) in the past year in order to participate in sports betting?</t>
+    <t>How often have you used online sportsbook applications (e.g., Draftkings, Fanduel, Bet MGM) in the past year in order to participate in sports betting?</t>
   </si>
   <si>
     <t>1=Often 2=Sometimes 3=Rarely 4=Never</t>
@@ -1447,7 +1450,12 @@
     <t>Display if “Yes” is selected for “Have you ever participated in sports betting?”</t>
   </si>
   <si>
-    <t>To what extent to which you agree or disagree with each of the following statements:I feel like sports betting controls my life. I have no problem setting limits on how much money I bet on sports.</t>
+    <t>To what extent to which you agree or disagree with each of the following statements:
+1. I feel like sports betting controls my life.
+2. I have no problem setting limits on how much money I bet on sports.</t>
+  </si>
+  <si>
+    <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Neither agree nor disagree 5=Somewhat disagree 6=Disagree 7=Strongly disagree</t>
   </si>
   <si>
     <t>Display if “Yes” is selected for “Have you ever participated in sports betting?” Matrix table with 2 statements.</t>
@@ -1457,13 +1465,26 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1486,9 +1507,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4628,15 +4653,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="255.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="223.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4652,36 +4676,13 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>449</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>450</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>52</v>
@@ -4692,36 +4693,13 @@
       <c r="E2" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
-      <c r="Z2" s="1"/>
-      <c r="AA2" s="1"/>
-      <c r="AB2" s="1"/>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>449</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>48</v>
+        <v>450</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>49</v>
@@ -4732,388 +4710,178 @@
       <c r="E3" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="1"/>
-      <c r="W3" s="1"/>
-      <c r="X3" s="1"/>
-      <c r="Y3" s="1"/>
-      <c r="Z3" s="1"/>
-      <c r="AA3" s="1"/>
-      <c r="AB3" s="1"/>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>449</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>48</v>
+        <v>450</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="1"/>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>449</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>48</v>
+        <v>450</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
-      <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
-      <c r="AB5" s="1"/>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>449</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>48</v>
+        <v>450</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="1"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
-      <c r="Z6" s="1"/>
-      <c r="AA6" s="1"/>
-      <c r="AB6" s="1"/>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>449</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
-      <c r="V7" s="1"/>
-      <c r="W7" s="1"/>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="1"/>
-      <c r="Z7" s="1"/>
-      <c r="AA7" s="1"/>
-      <c r="AB7" s="1"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>449</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1"/>
-      <c r="W8" s="1"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
-      <c r="Z8" s="1"/>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="1"/>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>449</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="1"/>
-      <c r="W9" s="1"/>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="1"/>
-      <c r="Z9" s="1"/>
-      <c r="AA9" s="1"/>
-      <c r="AB9" s="1"/>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>449</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-      <c r="V10" s="1"/>
-      <c r="W10" s="1"/>
-      <c r="X10" s="1"/>
-      <c r="Y10" s="1"/>
-      <c r="Z10" s="1"/>
-      <c r="AA10" s="1"/>
-      <c r="AB10" s="1"/>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>449</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="1"/>
-      <c r="X11" s="1"/>
-      <c r="Y11" s="1"/>
-      <c r="Z11" s="1"/>
-      <c r="AA11" s="1"/>
-      <c r="AB11" s="1"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="B12" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="C12" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="B13" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="D13" s="3" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="E13" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="B14" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>473</v>
       </c>
+      <c r="D14" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="F14" s="2"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/SurveyQuestions/csvs/hms_survey.xlsx
+++ b/SurveyQuestions/csvs/hms_survey.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" tabRatio="500" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" tabRatio="500" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Demographics" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="457">
   <si>
     <t>Module</t>
   </si>
@@ -602,9 +602,6 @@
     <t>In which venues was the death by suicide discussed or acknowledged? Select all that apply.</t>
   </si>
   <si>
-    <t>1=An official institutional communication (e.g., email, emergency alert system) 2=A memorial 3=News media (e.g., newspapers or blogs) 4=Social media (e.g., Reddit, Instagram, Meta, X) 5=Word of mouth from my peers 6=Other (please specify) 7=I don’t remember 8=None of these</t>
-  </si>
-  <si>
     <t>Thinking about the effect of the person’s suicide on your life, what response is closest to your experience?</t>
   </si>
   <si>
@@ -662,90 +659,60 @@
     <t>Specifically, which of the following depressive disorders were you diagnosed with by a professional? (Select all that apply)</t>
   </si>
   <si>
-    <t>1=Major depressive disorder 2=Dysthymia or persistent depressive disorder 3=Premenstrual dysphoric disorder 4=Other (please specify) 5=Don’t know</t>
-  </si>
-  <si>
     <t>Display if "1=Depression" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
   </si>
   <si>
     <t>Specifically, which of the following bipolar and related disorders were you diagnosed with by a professional? (Select all that apply)</t>
   </si>
   <si>
-    <t>1=Bipolar I disorder 2=Bipolar II disorder 3=Cyclothymic disorder 4=Other (please specify) 5=Don’t know</t>
-  </si>
-  <si>
     <t>Display if "2=Bipolar" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
   </si>
   <si>
     <t>Specifically, which of the following anxiety disorders were you diagnosed with by a professional? (Select all that apply)</t>
   </si>
   <si>
-    <t>1 =Generalized anxiety disorder 2=Panic disorder 3=Agoraphobia 4=Specific phobia (e.g., claustrophobia, arachnophobia, etc.) 5=Social anxiety disorder (or social phobia) 6=Other (please specify) 7=Don’t know</t>
-  </si>
-  <si>
     <t>Display if "3=Anxiety" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
   </si>
   <si>
     <t>Specifically, which of the following obsessive-compulsive or related disorders were you diagnosed with by a professional? (Select all that apply)</t>
   </si>
   <si>
-    <t>1=Obsessive-compulsive disorder 2=Body dysmorphic disorder 3=Hoarding disorder 4=Trichotillomania (hair-pulling disorder) 5=Excoriation (skin-picking) disorder 6=Other (please specify) 7=Don’t know</t>
-  </si>
-  <si>
     <t>Display if "4=Obsessive-compulsive or related disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
   </si>
   <si>
     <t>Specifically, which of the following trauma and stressor related disorders were you diagnosed with by a professional? (Select all that apply)</t>
   </si>
   <si>
-    <t>1=Post-traumatic stress disorder 2=Acute stress disorder 3=Adjustment disorder 4=Other (please specify) 5=Don’t know</t>
-  </si>
-  <si>
     <t>Display if "5=Trauma and Stressor Related Disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
   </si>
   <si>
     <t>Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)</t>
   </si>
   <si>
-    <t>1=Attention deficit hyperactivity disorder (ADHD or ADD) 2=Other intellectual disability 3=Autism spectrum disorder 4=Other (please specify) 5=Don’t know</t>
-  </si>
-  <si>
     <t>Display if "6=Neurodevelopmental disorder or intellectual disability" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
   </si>
   <si>
     <t>Specifically, which of the following eating disorders were you diagnosed with by a professional? (Select all that apply)</t>
   </si>
   <si>
-    <t>1=Anorexia nervosa 2=Bulimia nervosa 3=Binge-eating disorder 4=Pica 5=Avoidant/restrictive food intake disorder (selective eating disorder) 6=Other (please specify) 7=Don’t know</t>
-  </si>
-  <si>
     <t>Display if "7=Eating disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
   </si>
   <si>
     <t>Specifically, which of the following psychotic disorders were you diagnosed with by a professional? (Select all that apply)</t>
   </si>
   <si>
-    <t>1=Schizophrenia 2=Schizo-affective disorder 3=Brief psychotic disorder 4=Delusional disorder 5=Schizophreniform disorder 6=Other (please specify) 7=Don’t know</t>
-  </si>
-  <si>
     <t>Display if "8=Psychosis" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
   </si>
   <si>
     <t>Specifically, which of the following personality disorders were you diagnosed with by a professional? (Select all that apply)</t>
   </si>
   <si>
-    <t>1=Antisocial personality disorder 2=Avoidant personality disorder 3=Borderline personality disorder 4=Dependent personality disorder 5=Histrionic personality disorder 6=Narcissistic personality disorder 7=Obsessive-Compulsive personality disorder 8=Paranoid personality disorder 9=Schizoid personality disorder 10=Schizotypal personality disorder 11=Other (please specify) 12=Don’t know</t>
-  </si>
-  <si>
     <t>Display if "9=Personality disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
   </si>
   <si>
     <t>Specifically, which of the following substance disorders were you diagnosed with by a professional? (Select all that apply)</t>
   </si>
   <si>
-    <t>1=Alcohol abuse or other alcohol-related disorders 4=Opioid Use Disorder 2=Other (please specify) 3=Don’t know</t>
-  </si>
-  <si>
     <t>Display if "10=Substance use disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
   </si>
   <si>
@@ -755,9 +722,6 @@
     <t>Do you have a disability or disabilities from any of the following categories? (Select all that apply)</t>
   </si>
   <si>
-    <t>1=Attention deficit/hyperactivity disorders 2=Deaf or hard of hearing 3=Learning disorders 4=Mobility Impairments 5=Neurological disorders 6=Physical/health related disorders 7=Psychological disorder/condition 8=Visual impairments 9=Other (please specify) 10=Prefer not to respond [mutually exclusive] 11=I do not have a disability[mutually exclusive]</t>
-  </si>
-  <si>
     <t>Are you registered with the office for disability services/ADA office on this campus as having a disability?</t>
   </si>
   <si>
@@ -779,9 +743,6 @@
     <t>What type of treatment for ADHD have you received in the past year?</t>
   </si>
   <si>
-    <t>0=No treatment 1=Medication only 2=Therapy only (e.g., CBT for ADHD, Executive Function Coaching, etc.) 3=Medication and therapy 4=Other (please specify)</t>
-  </si>
-  <si>
     <t>Display if previous question is displayed</t>
   </si>
   <si>
@@ -827,9 +788,6 @@
     <t>If you were experiencing serious emotional distress, whom would you talk to about this? (Select all that apply)</t>
   </si>
   <si>
-    <t>1=Professional clinician (e.g., psychologist, counselor, or psychiatrist) 2=Roommate 3=Friend (who is not a roommate) 4=Significant other/romantic partner 5=Family member 6=Religious counselor or other religious contact 7=Support group 8=Other non-clinical source (please specify) 9=No one [mutually exclusive]</t>
-  </si>
-  <si>
     <t>Use of counseling/therapy</t>
   </si>
   <si>
@@ -860,9 +818,6 @@
     <t>From which of the following did you receive counseling or therapy in the past 12 months? (Select all that apply)</t>
   </si>
   <si>
-    <t>1=YourDost 2=Psychiatric Emergency Services/Psych Emergency Room (ER) 3=Inpatient psychiatric hospital 4=Partial hospitalization program 5=Provider in the local community (not on campus) 6=Provider in another location (such as your hometown) 7=Other</t>
-  </si>
-  <si>
     <t>Display only if “Are you currently receiving counseling or therapy” is displayed. Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
   </si>
   <si>
@@ -914,15 +869,9 @@
     <t>In the past 12 months have you taken any of the following types of prescription medications? (Please count only those you took, or are taking, several times per week.) (Select all that apply)</t>
   </si>
   <si>
-    <t>1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Other medication for mental or emotional health (please specify) 8=No, none of these [mutually exclusive] 9=Don’t know</t>
-  </si>
-  <si>
     <t>For what reason(s) do you use Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) ? (Select all that apply)</t>
   </si>
   <si>
-    <t>1=Mental or emotional health 2=Other health reasons 3=Academic performance 4=Recreation/fun 5=Other (please specify)</t>
-  </si>
-  <si>
     <t>If “1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexerdine), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
   </si>
   <si>
@@ -944,15 +893,9 @@
     <t>Who wrote your most recent prescription for the medication(s) you noted in the last question? (Select all that apply)</t>
   </si>
   <si>
-    <t>1=A general practitioner, nurse practitioner, or primary care physician 2=A psychiatrist 3=Other type of doctor (please specify) 4=Took the medication(s) without a prescription 5=Don’t know</t>
-  </si>
-  <si>
     <t>Of the medication(s) you just noted, which are you currently taking? (Select all that apply)</t>
   </si>
   <si>
-    <t>1=Psychostimulants (methylphenidate (Ritalin, or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Other medication for mental or emotional health (please specify) 8=None of the above [mutually exclusive]</t>
-  </si>
-  <si>
     <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
   </si>
   <si>
@@ -968,9 +911,6 @@
     <t>Where is the prescriber located who wrote most of the prescriptions for your stimulant in the past 12 months?</t>
   </si>
   <si>
-    <t>1=YourDost 2=Urgent Care or the Emergency Room 3=Provider in the local community (not on campus) 4=Provider in my hometown 5=Provider affiliated with a telehealth company 6=Other (please specify)</t>
-  </si>
-  <si>
     <t>Within the last 12 months, how has ADHD affected your academic performance?</t>
   </si>
   <si>
@@ -995,9 +935,6 @@
     <t>Which of the following are important reasons why you received those services? (Select all that apply)</t>
   </si>
   <si>
-    <t>1=I decided on my own to seek help. 2=A friend encouraged me to seek help. 3=A friend pressured me to seek help. 4=A family member encouraged me to seek help. 5=A family member pressured me to seek help. 6=Someone other than a friend or family member encouraged me to seek help (please specify the person's relationship to you). 7= A campus advisor mandated me to seek help 11= A campus advisor referred me to seek help 8=I acquired more information about my options from (please specify where). 10= A health professional recommended or referred me to seek help. 12=Other (please specify)</t>
-  </si>
-  <si>
     <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?" or "2=Yes, prior to starting at this school" is selected for "Have you ever received counseling or therapy for mental health concerns?" or "3=Yes, since starting at this school" is selected for "Have you ever received counseling or therapy for mental health concerns?" or "4=Yes, both of the above (prior to and since starting at this school)" is selected for "Have you ever received counseling or therapy for mental health concerns?"</t>
   </si>
   <si>
@@ -1007,24 +944,15 @@
     <t>In the past 12 months, which of the following factors have caused you to receive fewer services (counseling, therapy, or medications) for your mental or emotional health than you would have otherwise received? (Select all that apply)</t>
   </si>
   <si>
-    <t>1=No need for services 2=Financial reasons (too expensive, not covered by insurance) 3=Not enough time 4=Not sure where to go 5=Difficulty finding an available appointment 6=Prefer to deal with issues on my own or with support from family/friends 7=Privacy concerns 8= People providing services don’t understand me 9=Other (please specify) 10= No barriers [mutually exclusive] 11= fear of being mistreated due to my identity/identities 12=The clinic or clinician had limits on the number of times I could be seen</t>
-  </si>
-  <si>
     <t>In the past 12 months, which of the following explain why you have not received medication or therapy for your mental or emotional health? (Select all that apply)</t>
   </si>
   <si>
-    <t>1=I haven’t had the chance to go but I plan to. 2=No need for services 3=Financial reasons (too expensive, not covered by insurance) 4=Not enough time 5=Not sure where to go 6=Difficulty finding an available appointment 7=Prefer to deal with issues on my own or with support from family/friends 8=Other (please specify) 9=No barriers [mutually exclusive] 10=Privacy concerns 11=People providing services don’t understand me 12=Fear of being mistreated due to my identity/identities 13=The clinic or clinician had limits on the number of times I could be seen</t>
-  </si>
-  <si>
     <t>Informal help-seeking</t>
   </si>
   <si>
     <t>In the past 12 months have you received support for your mental or emotional health from any of the following sources? (Select all that apply)</t>
   </si>
   <si>
-    <t>1=Roommate 2=Friend (who is not a roommate) 3=Significant other 4=Family member 5=Religious counselor or other religious contact 6=Support group 9=Faculty member/professor/instructor 10=Staff member 7=Other non-clinical source (please specify) 8=No, none of these [mutually exclusive]</t>
-  </si>
-  <si>
     <t>How helpful was it to discuss these concerns?</t>
   </si>
   <si>
@@ -1034,9 +962,6 @@
     <t>If you had a mental health problem that you believed was affecting your academic performance, which people at your school would you talk to? (Select all that apply)</t>
   </si>
   <si>
-    <t>1=Professor/Instructor from one of my classes 2=Academic advisor/academic counselor 3=Another faculty member or instructor 4=Teaching assistant 5=Student services staff 6=Dean of Students or class dean 7=Other (please specify) 8=No one [mutually exclusive]</t>
-  </si>
-  <si>
     <t>During this school year have you talked with any academic personnel (such as instructors, advisors, or other academic staff) about any mental health problems that were affecting your academic performance?</t>
   </si>
   <si>
@@ -1079,9 +1004,6 @@
     <t>I feel that coverage is inadequate because my plan… (Select all that apply)</t>
   </si>
   <si>
-    <t>1=…doesn’t cover any mental health services. 2=…doesn’t cover pre existing conditions. 3=…doesn’t cover certain conditions. 4=…has a co-pay that is too expensive. 5=…has a deductible that is too expensive. 6=…doesn’t cover certain types of services or providers. 7=…has a limit on the number of services that are covered. 8=Other (please specify)</t>
-  </si>
-  <si>
     <t>Display if “No, the coverage is inadequate to meet my needs” is selected for “Does your current health insurance plan meet your needs for mental health services?”</t>
   </si>
   <si>
@@ -1103,18 +1025,12 @@
     <t>Have you ever been diagnosed with any of the following health conditions, which required ongoing treatment by a healthcare professional (i.e., chronic diseases)? (Select all that apply)</t>
   </si>
   <si>
-    <t>1=Diabetes 2=High blood pressure 3=Asthma 4=Thyroid disease (e.g., hypothyroid or hyperthyroid) 5=Gastrointestinal disease (e.g., Crohn’s Disease, Ulcerative Colitis) 6=Arthritis 7=Sickle cell anemia 8=Seizure disorders (e.g., epilepsy) 9=Cancers 10=High cholesterol 11=HIV/AIDS 12=Other autoimmune disorder (please specify) 13=Other chronic disease (please specify) 14=No, never been diagnosed with a chronic disease. [mutually exclusive] 15=Don’t know [mutually exclusive]</t>
-  </si>
-  <si>
     <t>How much do you agree with the following statement?: My exercise habits have changed a lot since I began as a student at my school.</t>
   </si>
   <si>
     <t>How have your exercise habits changed since you began as a student at your school?</t>
   </si>
   <si>
-    <t>1=I exercise more now. 2=I exercise less now. 3=Other (please specify)</t>
-  </si>
-  <si>
     <t>Display if selected “strongly agree”, “agree”, or “somewhat disagree” for “My exercise habits have changed a lot since I began as a student at my school” Instructions: “For these next questions, please think about injuries you have had during your entire lifetime, especially those that affected your head or neck. It might</t>
   </si>
   <si>
@@ -1127,9 +1043,6 @@
     <t>0=No 1=Yes 2=I don’t know 3=Prefer not to say</t>
   </si>
   <si>
-    <t>help to remember times you went to the hospital or</t>
-  </si>
-  <si>
     <t>Thinking about any injuries to your head or neck that you have had in your lifetime, were you ever dazed or have a gap in your memory from any of the injuries?</t>
   </si>
   <si>
@@ -1169,9 +1082,6 @@
     <t>Why did you become vegan or vegetarian? (Select all that apply)</t>
   </si>
   <si>
-    <t>1= To improve my overall health. 2= To manage a specific health condition. 3= To lose weight. 4= To spend less money on food. 5= To reduce my carbon footprint or protect the environment. 6=Other (text)</t>
-  </si>
-  <si>
     <t>Display if "1=Yes" is selected for "Do the following eating practices apply to you?: I am vegan." or "1=Yes" is selected for "Do the following eating practices apply to you?: I am vegetarian."</t>
   </si>
   <si>
@@ -1194,60 +1104,6 @@
   </si>
   <si>
     <t>Definition from American Heart Association 2014</t>
-  </si>
-  <si>
-    <t>Sexual health and behavior</t>
-  </si>
-  <si>
-    <t>How many people have you had sexual contact with in the past 12 months?</t>
-  </si>
-  <si>
-    <t>1=0 2=1 3=2 4=3 5=4 6=5-9 7=10 or more</t>
-  </si>
-  <si>
-    <t>In the past 30 days, what type of birth control method(s) did you or your partner(s) use during or for sexual intercourse? (Select all that apply)</t>
-  </si>
-  <si>
-    <t>1=Male condom 13=Internal/female condom 2=Withdrawal (i.e., “pulling out”) 3=Contraceptive pills 4=Contraceptive patch 5=Contraceptive ring (e.g., Nuvaring) 6=Contraceptive injectable (e.g., Depo-Provera shot) 7=Intrauterine device (IUD) 8=Contraceptive implant (e.g., implanon/nexplanon) 9=Emergency contraception (i.e., “morning after pill”) 10=Other contraceptive method (please specify) 11=No contraceptive method was used [mutually exclusive] 12=Don’t know</t>
-  </si>
-  <si>
-    <t>For what reason(s) did you or your partner(s) not use contraception in the past 30 days? (Select all that apply)</t>
-  </si>
-  <si>
-    <t>1=No pregnancy risk (including infertility/sterility, being the same sex as your partner(s), etc.) 2=Lack of access to birth control methods 3=Lack of access to information about birth control methods 4=You or your partner(s) didn’t want to use birth control (including barrier methods, hormonal contraception, etc) 5=You or your partner(s) can’t be on hormonal birth control for medical reasons 6=You or your partner(s) are trying to get pregnant 7=Some other reason</t>
-  </si>
-  <si>
-    <t>If “11=No contraceptive method was used” was selected for “In the past 30 days, what type of birth control method did you or your partner(s) use?</t>
-  </si>
-  <si>
-    <t>In the past 30 days, did you or your partner(s) use some form of birth control or protection (e.g. condoms, birth control pills) every single time you had sex?</t>
-  </si>
-  <si>
-    <t>1=Yes 2=No 3=Don’t know</t>
-  </si>
-  <si>
-    <t>If “11=No contraceptive method was used” was NOT selected for “In the past 30 days, what type of birth control method did you or your partner(s) use?</t>
-  </si>
-  <si>
-    <t>Which of the following “safer sex” practices did/do you and your partner(s) use to prevent STIs, if any? (Select all that apply)</t>
-  </si>
-  <si>
-    <t>1=Barrier methods (condoms, dental dams, etc.) 2=Regular STI testing 3=Monogamy 4=Pr EP for HIV prevention 5=Other safer sex practices (please specify) 6=None of these [mutually exclusive]</t>
-  </si>
-  <si>
-    <t>Have you or a sexual partner (current or past) ever become pregnant? (Select all that apply)</t>
-  </si>
-  <si>
-    <t>1=No [mutually exclusive] 2=Yes, unintentionally 3=Yes, intentionally 4=Don’t know</t>
-  </si>
-  <si>
-    <t>Have you been pregnant or given birth within the last 12 months?</t>
-  </si>
-  <si>
-    <t>1=Yes 2=No 3=Prefer not to say 4=I don’t know</t>
-  </si>
-  <si>
-    <t>Do not display if “1=No” was selected for “Have you or a sexual partner (current or past) ever become pregnant?” Do not display if “2=Male” is selected for “What sex were you assigned at birth?”</t>
   </si>
   <si>
     <t>Academic Persistence, Retention and Competition</t>
@@ -1315,15 +1171,9 @@
     <t>Which of the following challenges are most likely to prevent you from finishing your degree? (Select all that apply)</t>
   </si>
   <si>
-    <t>1=Financial challenges 2=Mental or emotional health problems 3=Other health problems (not directly related to mental or emotional health) 4=Family obligations 5=Family or relationship difficulties 6=Academic challenges (struggling to pass classes) 7=[if not U.S. citizen, ask→Visa or other challenges related to being a non-U.S. citizen] 8=Lack of motivation or desire 9=Work or professional commitments 10=Career opportunities 11=Other challenge(s) (please specify)</t>
-  </si>
-  <si>
     <t>What is the highest degree you plan to pursue?</t>
   </si>
   <si>
-    <t>1=2-year college degree (associate’s) 2=4-year college degree (bachelor’s) 3=Master’s degree 4=Doctoral degree (JD, MD, Ph D, etc.) 5=Other degree (please specify) 6=Don’t know</t>
-  </si>
-  <si>
     <t>How much do you agree with the following statements? I have doubts about whether higher education is worth the time, money, and effort that I’m spending on it. My family is very supportive of my educational goals. My professors believe in my potential to succeed academically.</t>
   </si>
   <si>
@@ -1417,9 +1267,6 @@
     <t>Which of the following have you used to pay for educational expenses (room, board, tuition, and fees)? (Select all that apply)</t>
   </si>
   <si>
-    <t>1=Family resources (parents, relatives, spouse, etc.) 2=Your own resources (income from work, work-study, etc.) 3=Aid that need not be repaid (grants, scholarships, military, etc.) 4=Aid that must be repaid (loans) 5=Other sources (please specify)</t>
-  </si>
-  <si>
     <t>Financing education</t>
   </si>
   <si>
@@ -1430,9 +1277,6 @@
   </si>
   <si>
     <t>Do you receive scholarship funding from your institution? (Select all that apply)</t>
-  </si>
-  <si>
-    <t>1=No [mutually exclusive] 2=Yes, a need based scholarship 3=Yes, an academic scholarship (or merit scholarship) 4=Yes, an athletic scholarship 5=Other (please specify)</t>
   </si>
   <si>
     <t>Spending</t>
@@ -1459,6 +1303,105 @@
   </si>
   <si>
     <t>Display if “Yes” is selected for “Have you ever participated in sports betting?” Matrix table with 2 statements.</t>
+  </si>
+  <si>
+    <t>1=Family resources (parents, relatives, spouse, etc.) 2=Your own resources (income from work, work-study, etc.) 3=Aid that need not be repaid (grants, scholarships, military, etc.) 4=Aid that must be repaid (loans) 5=Other sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1=No [mutually exclusive] 2=Yes, a need based scholarship 3=Yes, an academic scholarship (or merit scholarship) 4=Yes, an athletic scholarship 5=Other </t>
+  </si>
+  <si>
+    <t>1=Financial challenges 2=Mental or emotional health problems 3=Other health problems (not directly related to mental or emotional health) 4=Family obligations 5=Family or relationship difficulties 6=Academic challenges (struggling to pass classes) 7=Lack of motivation or desire 8=Work or professional commitments 9=Career opportunities 10=Others</t>
+  </si>
+  <si>
+    <t>1=2-year college degree (associate’s) 2=4-year college degree (bachelor’s) 3=Master’s degree 4=Doctoral degree (JD, MD, Ph D, etc.) 5=Other degree  6=Don’t know</t>
+  </si>
+  <si>
+    <t>1=An official institutional communication (e.g., email, emergency alert system) 2=A memorial 3=News media (e.g., newspapers or blogs) 4=Social media (e.g., Reddit, Instagram, Meta, X) 5=Word of mouth from my peers 6=Others  7=I don’t remember 8=None of these</t>
+  </si>
+  <si>
+    <t>1=Major depressive disorder 2=Dysthymia or persistent depressive disorder 3=Premenstrual dysphoric disorder 4=Others  5=Don’t know</t>
+  </si>
+  <si>
+    <t>1=Bipolar I disorder 2=Bipolar II disorder 3=Cyclothymic disorder 4=Others  5=Don’t know</t>
+  </si>
+  <si>
+    <t>1 =Generalized anxiety disorder 2=Panic disorder 3=Agoraphobia 4=Specific phobia (e.g., claustrophobia, arachnophobia, etc.) 5=Social anxiety disorder (or social phobia) 6=Others  7=Don’t know</t>
+  </si>
+  <si>
+    <t>1=Obsessive-compulsive disorder 2=Body dysmorphic disorder 3=Hoarding disorder 4=Trichotillomania (hair-pulling disorder) 5=Excoriation (skin-picking) disorder 6=Others 7=Don’t know</t>
+  </si>
+  <si>
+    <t>1=Post-traumatic stress disorder 2=Acute stress disorder 3=Adjustment disorder 4=Others  5=Don’t know</t>
+  </si>
+  <si>
+    <t>1=Attention deficit hyperactivity disorder (ADHD or ADD) 2=Other intellectual disability 3=Autism spectrum disorder 4=Others  5=Don’t know</t>
+  </si>
+  <si>
+    <t>1=Anorexia nervosa 2=Bulimia nervosa 3=Binge-eating disorder 4=Pica 5=Avoidant/restrictive food intake disorder (selective eating disorder) 6=Others 7=Don’t know</t>
+  </si>
+  <si>
+    <t>1=Schizophrenia 2=Schizo-affective disorder 3=Brief psychotic disorder 4=Delusional disorder 5=Schizophreniform disorder 6=Others  7=Don’t know</t>
+  </si>
+  <si>
+    <t>1=Antisocial personality disorder 2=Avoidant personality disorder 3=Borderline personality disorder 4=Dependent personality disorder 5=Histrionic personality disorder 6=Narcissistic personality disorder 7=Obsessive-Compulsive personality disorder 8=Paranoid personality disorder 9=Schizoid personality disorder 10=Schizotypal personality disorder 11=Others 12=Don’t know</t>
+  </si>
+  <si>
+    <t>1=Alcohol abuse or other alcohol-related disorders 4=Opioid Use Disorder 2=Others  3=Don’t know</t>
+  </si>
+  <si>
+    <t>1=Attention deficit/hyperactivity disorders 2=Deaf or hard of hearing 3=Learning disorders 4=Mobility Impairments 5=Neurological disorders 6=Physical/health related disorders 7=Psychological disorder/condition 8=Visual impairments 9=Others 10=Prefer not to respond [mutually exclusive] 11=I do not have a disability[mutually exclusive]</t>
+  </si>
+  <si>
+    <t>0=No treatment 1=Medication only 2=Therapy only (e.g., CBT for ADHD, Executive Function Coaching, etc.) 3=Medication and therapy 4=Others</t>
+  </si>
+  <si>
+    <t>1=Professional clinician (e.g., psychologist, counselor, or psychiatrist) 2=Roommate 3=Friend (who is not a roommate) 4=Significant other/romantic partner 5=Family member 6=Religious counselor or other religious contact 7=Support group 8=Other non-clinical source 9=No one [mutually exclusive]</t>
+  </si>
+  <si>
+    <t>1=YourDost 2=Psychiatric Emergency Services/Psych Emergency Room (ER) 3=Inpatient psychiatric hospital 4=Partial hospitalization program 5=Provider in the local community (not on campus) 6=Provider in another location (such as your hometown) 7=Others</t>
+  </si>
+  <si>
+    <t>1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Others  8=No, none of these [mutually exclusive] 9=Don’t know</t>
+  </si>
+  <si>
+    <t>1=Mental or emotional health 2=Other health reasons 3=Academic performance 4=Recreation/fun 5=Others</t>
+  </si>
+  <si>
+    <t>1=A general practitioner, nurse practitioner, or primary care physician 2=A psychiatrist 3=Other type of doctor  4=Took the medication(s) without a prescription 5=Don’t know</t>
+  </si>
+  <si>
+    <t>1=Psychostimulants (methylphenidate (Ritalin, or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Other medication for mental or emotional health  8=None of the above [mutually exclusive]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1=YourDost 2=Urgent Care or the Emergency Room 3=Provider in the local community (not on campus) 4=Provider in my hometown 5=Provider affiliated with a telehealth company 6=Other </t>
+  </si>
+  <si>
+    <t>1=I decided on my own to seek help. 2=A friend encouraged me to seek help. 3=A friend pressured me to seek help. 4=A family member encouraged me to seek help. 5=A family member pressured me to seek help. 6=Someone other than a friend or family member encouraged me to seek help  7= A campus advisor mandated me to seek help 11= A campus advisor referred me to seek help 8=I acquired more information about my options from  10= A health professional recommended or referred me to seek help. 12=Other (please specify)</t>
+  </si>
+  <si>
+    <t>1=No need for services 2=Financial reasons (too expensive, not covered by insurance) 3=Not enough time 4=Not sure where to go 5=Difficulty finding an available appointment 6=Prefer to deal with issues on my own or with support from family/friends 7=Privacy concerns 8= People providing services don’t understand me 9=Other 10= No barriers [mutually exclusive] 11= fear of being mistreated due to my identity/identities 12=The clinic or clinician had limits on the number of times I could be seen</t>
+  </si>
+  <si>
+    <t>1=I haven’t had the chance to go but I plan to. 2=No need for services 3=Financial reasons (too expensive, not covered by insurance) 4=Not enough time 5=Not sure where to go 6=Difficulty finding an available appointment 7=Prefer to deal with issues on my own or with support from family/friends 8=Others  9=No barriers [mutually exclusive] 10=Privacy concerns 11=People providing services don’t understand me 12=Fear of being mistreated due to my identity/identities 13=The clinic or clinician had limits on the number of times I could be seen</t>
+  </si>
+  <si>
+    <t>1=Roommate 2=Friend (who is not a roommate) 3=Significant other 4=Family member 5=Religious counselor or other religious contact 6=Support group 9=Faculty member/professor/instructor 10=Staff member 7=Other non-clinical source  8=No, none of these [mutually exclusive]</t>
+  </si>
+  <si>
+    <t>1=Professor/Instructor from one of my classes 2=Academic advisor/academic counselor 3=Another faculty member or instructor 4=Teaching assistant 5=Student services staff 6=Dean of Students or class dean 7=Others  8=No one [mutually exclusive]</t>
+  </si>
+  <si>
+    <t>1=…doesn’t cover any mental health services. 2=…doesn’t cover pre existing conditions. 3=…doesn’t cover certain conditions. 4=…has a co-pay that is too expensive. 5=…has a deductible that is too expensive. 6=…doesn’t cover certain types of services or providers. 7=…has a limit on the number of services that are covered. 8=Others</t>
+  </si>
+  <si>
+    <t>1=Diabetes 2=High blood pressure 3=Asthma 4=Thyroid disease (e.g., hypothyroid or hyperthyroid) 5=Gastrointestinal disease (e.g., Crohn’s Disease, Ulcerative Colitis) 6=Arthritis 7=Sickle cell anemia 8=Seizure disorders (e.g., epilepsy) 9=Cancers 10=High cholesterol 11=HIV/AIDS 12=Other autoimmune disorder  13=Other chronic disease  14=No, never been diagnosed with a chronic disease. [mutually exclusive] 15=Don’t know [mutually exclusive]</t>
+  </si>
+  <si>
+    <t>1=I exercise more now. 2=I exercise less now. 3=Others</t>
+  </si>
+  <si>
+    <t>1= To improve my overall health. 2= To manage a specific health condition. 3= To lose weight. 4= To spend less money on food. 5= To reduce my carbon footprint or protect the environment. 6=Others</t>
   </si>
 </sst>
 </file>
@@ -2970,7 +2913,7 @@
         <v>191</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>192</v>
+        <v>428</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>188</v>
@@ -2984,10 +2927,10 @@
         <v>183</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>188</v>
@@ -3001,10 +2944,10 @@
         <v>183</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>188</v>
@@ -3015,13 +2958,13 @@
         <v>118</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3029,16 +2972,16 @@
         <v>118</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3046,16 +2989,16 @@
         <v>118</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="1048567" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3098,313 +3041,313 @@
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C3" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>215</v>
+        <v>430</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>218</v>
+        <v>431</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C6" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>221</v>
+        <v>432</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C7" s="1" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>224</v>
+        <v>433</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C8" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>227</v>
+        <v>434</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C9" s="1" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>230</v>
+        <v>435</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C10" s="1" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>233</v>
+        <v>436</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C11" s="1" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>236</v>
+        <v>437</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C12" s="1" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>239</v>
+        <v>438</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>243</v>
+        <v>439</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>251</v>
+        <v>440</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>90</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>90</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>90</v>
@@ -3412,477 +3355,477 @@
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>90</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>267</v>
+        <v>441</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>278</v>
+        <v>442</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>296</v>
+        <v>443</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>298</v>
+        <v>444</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>298</v>
+        <v>444</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>306</v>
+        <v>445</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>308</v>
+        <v>446</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>309</v>
+        <v>290</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>111</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>111</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="D40" s="1" t="s">
-        <v>314</v>
+        <v>447</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>309</v>
+        <v>290</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>322</v>
+        <v>302</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>323</v>
+        <v>448</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>324</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>327</v>
+        <v>449</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>328</v>
+        <v>306</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>329</v>
+        <v>450</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>330</v>
+        <v>307</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>332</v>
+        <v>451</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>330</v>
+        <v>307</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>334</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>330</v>
+        <v>307</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>336</v>
+        <v>452</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>29</v>
@@ -3890,104 +3833,104 @@
     </row>
     <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>330</v>
+        <v>307</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>338</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>330</v>
+        <v>307</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>339</v>
+        <v>314</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>340</v>
+        <v>315</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>341</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>342</v>
+        <v>317</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>343</v>
+        <v>318</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>344</v>
+        <v>319</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>338</v>
+        <v>313</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>342</v>
+        <v>317</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>345</v>
+        <v>320</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>347</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>342</v>
+        <v>317</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>348</v>
+        <v>323</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>349</v>
+        <v>324</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>347</v>
+        <v>322</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>342</v>
+        <v>317</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>350</v>
+        <v>325</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>351</v>
+        <v>453</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>352</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -4000,6 +3943,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E24"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="63" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -4020,35 +3966,35 @@
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>354</v>
+        <v>328</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>355</v>
+        <v>329</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>356</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>357</v>
+        <v>331</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>358</v>
+        <v>332</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>359</v>
+        <v>454</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>173</v>
@@ -4062,13 +4008,13 @@
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>173</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>360</v>
+        <v>333</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>90</v>
@@ -4076,183 +4022,179 @@
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>173</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>361</v>
+        <v>334</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>362</v>
+        <v>455</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>363</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>364</v>
+        <v>336</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>365</v>
+        <v>337</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>367</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>364</v>
+        <v>336</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>368</v>
+        <v>339</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>367</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>364</v>
+        <v>336</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>370</v>
+        <v>341</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>371</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>364</v>
+        <v>336</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>373</v>
+        <v>344</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>374</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>364</v>
+        <v>336</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>375</v>
+        <v>346</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>370</v>
+        <v>341</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>374</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>376</v>
+        <v>347</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>377</v>
+        <v>348</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>378</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>376</v>
+        <v>347</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>379</v>
+        <v>350</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>378</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>376</v>
+        <v>347</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>380</v>
+        <v>351</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>381</v>
+        <v>456</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>382</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>383</v>
-      </c>
       <c r="D15" s="1" t="s">
-        <v>384</v>
+        <v>354</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>385</v>
+        <v>355</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>376</v>
+        <v>347</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>386</v>
+        <v>356</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>26</v>
@@ -4260,128 +4202,28 @@
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>376</v>
+        <v>347</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>388</v>
+        <v>358</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
+        <v>359</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4412,95 +4254,95 @@
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>408</v>
+        <v>360</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>409</v>
+        <v>361</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>410</v>
+        <v>362</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>411</v>
+        <v>363</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>412</v>
+        <v>364</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>408</v>
+        <v>360</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>413</v>
+        <v>365</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>414</v>
+        <v>366</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>415</v>
+        <v>367</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>416</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>408</v>
+        <v>360</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>413</v>
+        <v>365</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>417</v>
+        <v>369</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>418</v>
+        <v>370</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>408</v>
+        <v>360</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>419</v>
+        <v>371</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>420</v>
+        <v>372</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>411</v>
+        <v>363</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>421</v>
+        <v>373</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>408</v>
+        <v>360</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>422</v>
+        <v>374</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>423</v>
+        <v>375</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>411</v>
+        <v>363</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>424</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>408</v>
+        <v>360</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>425</v>
+        <v>377</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>426</v>
+        <v>378</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>90</v>
@@ -4508,41 +4350,41 @@
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>408</v>
+        <v>360</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>425</v>
+        <v>377</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>427</v>
+        <v>379</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>408</v>
+        <v>360</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>425</v>
+        <v>377</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>429</v>
+        <v>380</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>408</v>
+        <v>360</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>425</v>
+        <v>377</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>431</v>
+        <v>381</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>90</v>
@@ -4550,27 +4392,27 @@
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>408</v>
+        <v>360</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>425</v>
+        <v>377</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>432</v>
+        <v>382</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>433</v>
+        <v>383</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>408</v>
+        <v>360</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>425</v>
+        <v>377</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>434</v>
+        <v>384</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>26</v>
@@ -4581,67 +4423,67 @@
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>408</v>
+        <v>360</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>435</v>
+        <v>385</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>436</v>
+        <v>386</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>437</v>
+        <v>387</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>438</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>408</v>
+        <v>360</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>439</v>
+        <v>389</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>440</v>
+        <v>390</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>441</v>
+        <v>391</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>442</v>
+        <v>392</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>408</v>
+        <v>360</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>443</v>
+        <v>393</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>444</v>
+        <v>394</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>433</v>
+        <v>383</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>408</v>
+        <v>360</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>445</v>
+        <v>395</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>446</v>
+        <v>396</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>447</v>
+        <v>397</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>448</v>
+        <v>398</v>
       </c>
     </row>
     <row r="1048576" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4657,7 +4499,7 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="39.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="71.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4679,10 +4521,10 @@
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>449</v>
+        <v>399</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>52</v>
@@ -4691,15 +4533,15 @@
         <v>50</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>449</v>
+        <v>399</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>49</v>
@@ -4708,60 +4550,60 @@
         <v>50</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>449</v>
+        <v>399</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>451</v>
+        <v>401</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>452</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>449</v>
+        <v>399</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>453</v>
+        <v>403</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>452</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>449</v>
+        <v>399</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>454</v>
+        <v>404</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>455</v>
+        <v>405</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>449</v>
+        <v>399</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>456</v>
+        <v>406</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>457</v>
+        <v>407</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>111</v>
@@ -4769,44 +4611,44 @@
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>449</v>
+        <v>399</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>456</v>
+        <v>406</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>458</v>
+        <v>408</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>459</v>
+        <v>409</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>460</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>449</v>
+        <v>399</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>456</v>
+        <v>406</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>461</v>
+        <v>411</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>462</v>
+        <v>424</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>449</v>
+        <v>399</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>463</v>
+        <v>412</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>464</v>
+        <v>413</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>90</v>
@@ -4814,27 +4656,27 @@
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>449</v>
+        <v>399</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>465</v>
+        <v>414</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>466</v>
+        <v>415</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>467</v>
+        <v>425</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>449</v>
+        <v>399</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>468</v>
+        <v>416</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>469</v>
+        <v>417</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
@@ -4846,37 +4688,37 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>449</v>
+        <v>399</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>468</v>
+        <v>416</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>470</v>
+        <v>418</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>471</v>
+        <v>419</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>472</v>
+        <v>420</v>
       </c>
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>449</v>
+        <v>399</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>468</v>
+        <v>416</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>474</v>
+        <v>422</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>475</v>
+        <v>423</v>
       </c>
       <c r="F14" s="2"/>
     </row>

--- a/SurveyQuestions/csvs/hms_survey.xlsx
+++ b/SurveyQuestions/csvs/hms_survey.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" tabRatio="500" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" tabRatio="500" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Demographics" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="456">
   <si>
     <t>Module</t>
   </si>
@@ -821,9 +821,6 @@
     <t>Display only if “Are you currently receiving counseling or therapy” is displayed. Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
   </si>
   <si>
-    <t>Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted? [pipe in selected options from the question, “From which of the following places did you receive counseling or therapy?”]</t>
-  </si>
-  <si>
     <t>1=In-person only 2=Remote/telehealth only (digital video conferencing, text/app chat, etc…) 3=Both in-person and remote</t>
   </si>
   <si>
@@ -1086,9 +1083,6 @@
   </si>
   <si>
     <t>Of the reasons selected above, which one is the most important or primary reason for becoming vegan or vegetarian?</t>
-  </si>
-  <si>
-    <t>1= To improve my overall health. 2= To manage a specific health condition. 3= To lose weight. 4= To spend less money on food. 5= To reduce my carbon footprint or protect the environment. 6=Other</t>
   </si>
   <si>
     <t>Display if reasons selected for "Why did you become vegan or vegetarian?"</t>
@@ -1222,9 +1216,6 @@
     <t>In the past year, how has the following affected your academic performance? (Select all that apply) Anxiety/stress Depression/suicidality Eating/body image concerns Attention disorder or learning disability (e.g., attention deficit disorder, attention deficit hyperactivity disorder, learning disability) Alcohol/substance use Physical health condition Physical assault Sexual assault</t>
   </si>
   <si>
-    <t>1=I did not experience this. 2=I experienced this but it did not affect my academic performance. 3=I received a lower grade on one or more exams or projects. 4=I received a lower grade in one or more courses. 5=I received an incomplete or dropped one or more courses. 6=I had a significant disruption in research, practicum, thesis, or dissertation work. 7=Other (please specify)</t>
-  </si>
-  <si>
     <t>Matrix table with 8 factors. Adapted from American College Health Association’s National College Health Assessment</t>
   </si>
   <si>
@@ -1255,12 +1246,6 @@
     <t>Do you have any concerns about your current living situation, like housing conditions, safety, and costs?</t>
   </si>
   <si>
-    <t>What are those concerns? (Select all that apply.</t>
-  </si>
-  <si>
-    <t>1=Condition/quality of housing 2=Lack of more permanent housing 3=Ability to pay for housing or utilities 4=Feeling safe 5=Other (please specify)</t>
-  </si>
-  <si>
     <t>Display if “Yes” is selected for “Do you have any concerns about your current living situation, like housing conditions, safety, and costs?”</t>
   </si>
   <si>
@@ -1283,9 +1268,6 @@
   </si>
   <si>
     <t>Have you ever participated in sports betting?</t>
-  </si>
-  <si>
-    <t>How often have you used online sportsbook applications (e.g., Draftkings, Fanduel, Bet MGM) in the past year in order to participate in sports betting?</t>
   </si>
   <si>
     <t>1=Often 2=Sometimes 3=Rarely 4=Never</t>
@@ -1308,9 +1290,6 @@
     <t>1=Family resources (parents, relatives, spouse, etc.) 2=Your own resources (income from work, work-study, etc.) 3=Aid that need not be repaid (grants, scholarships, military, etc.) 4=Aid that must be repaid (loans) 5=Other sources</t>
   </si>
   <si>
-    <t xml:space="preserve">1=No [mutually exclusive] 2=Yes, a need based scholarship 3=Yes, an academic scholarship (or merit scholarship) 4=Yes, an athletic scholarship 5=Other </t>
-  </si>
-  <si>
     <t>1=Financial challenges 2=Mental or emotional health problems 3=Other health problems (not directly related to mental or emotional health) 4=Family obligations 5=Family or relationship difficulties 6=Academic challenges (struggling to pass classes) 7=Lack of motivation or desire 8=Work or professional commitments 9=Career opportunities 10=Others</t>
   </si>
   <si>
@@ -1377,9 +1356,6 @@
     <t xml:space="preserve">1=YourDost 2=Urgent Care or the Emergency Room 3=Provider in the local community (not on campus) 4=Provider in my hometown 5=Provider affiliated with a telehealth company 6=Other </t>
   </si>
   <si>
-    <t>1=I decided on my own to seek help. 2=A friend encouraged me to seek help. 3=A friend pressured me to seek help. 4=A family member encouraged me to seek help. 5=A family member pressured me to seek help. 6=Someone other than a friend or family member encouraged me to seek help  7= A campus advisor mandated me to seek help 11= A campus advisor referred me to seek help 8=I acquired more information about my options from  10= A health professional recommended or referred me to seek help. 12=Other (please specify)</t>
-  </si>
-  <si>
     <t>1=No need for services 2=Financial reasons (too expensive, not covered by insurance) 3=Not enough time 4=Not sure where to go 5=Difficulty finding an available appointment 6=Prefer to deal with issues on my own or with support from family/friends 7=Privacy concerns 8= People providing services don’t understand me 9=Other 10= No barriers [mutually exclusive] 11= fear of being mistreated due to my identity/identities 12=The clinic or clinician had limits on the number of times I could be seen</t>
   </si>
   <si>
@@ -1402,6 +1378,27 @@
   </si>
   <si>
     <t>1= To improve my overall health. 2= To manage a specific health condition. 3= To lose weight. 4= To spend less money on food. 5= To reduce my carbon footprint or protect the environment. 6=Others</t>
+  </si>
+  <si>
+    <t>What are those concerns? (Select all that apply)</t>
+  </si>
+  <si>
+    <t>1=Condition/quality of housing 2=Lack of more permanent housing 3=Ability to pay for housing or utilities 4=Feeling safe 5=Others</t>
+  </si>
+  <si>
+    <t>1=No [mutually exclusive] 2=Yes, a need based scholarship 3=Yes, an academic scholarship (or merit scholarship) 4=Yes, an athletic scholarship 5=Others</t>
+  </si>
+  <si>
+    <t>How often have you used online sportsbook applications (e.g., Dream11,Parimatch,Dafabet) in the past year in order to participate in sports betting?</t>
+  </si>
+  <si>
+    <t>1=I did not experience this. 2=I experienced this but it did not affect my academic performance. 3=I received a lower grade on one or more exams or projects. 4=I received a lower grade in one or more courses. 5=I received an incomplete or dropped one or more courses. 6=I had a significant disruption in research, practicum, thesis, or dissertation work. 7=Others</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted? </t>
+  </si>
+  <si>
+    <t>1=I decided on my own to seek help. 2=A friend encouraged me to seek help. 3=A friend pressured me to seek help. 4=A family member encouraged me to seek help. 5=A family member pressured me to seek help. 6=Someone other than a friend or family member encouraged me to seek help  7= A campus advisor mandated me to seek help 11= A campus advisor referred me to seek help 8=I acquired more information about my options from  10= A health professional recommended or referred me to seek help. 12=Others</t>
   </si>
 </sst>
 </file>
@@ -1450,12 +1447,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2913,7 +2913,7 @@
         <v>191</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>188</v>
@@ -3064,7 +3064,7 @@
         <v>210</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>211</v>
@@ -3081,7 +3081,7 @@
         <v>212</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>213</v>
@@ -3098,7 +3098,7 @@
         <v>214</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>215</v>
@@ -3115,7 +3115,7 @@
         <v>216</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>217</v>
@@ -3132,7 +3132,7 @@
         <v>218</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>219</v>
@@ -3149,7 +3149,7 @@
         <v>220</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>221</v>
@@ -3166,7 +3166,7 @@
         <v>222</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>223</v>
@@ -3183,7 +3183,7 @@
         <v>224</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>225</v>
@@ -3200,7 +3200,7 @@
         <v>226</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>227</v>
@@ -3217,7 +3217,7 @@
         <v>228</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>229</v>
@@ -3234,7 +3234,7 @@
         <v>231</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3282,7 +3282,7 @@
         <v>238</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>239</v>
@@ -3299,7 +3299,7 @@
         <v>240</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>241</v>
@@ -3381,7 +3381,7 @@
         <v>253</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3446,7 +3446,7 @@
         <v>263</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>264</v>
@@ -3460,13 +3460,13 @@
         <v>254</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3474,16 +3474,16 @@
         <v>206</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3491,16 +3491,16 @@
         <v>206</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3508,16 +3508,16 @@
         <v>206</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3525,16 +3525,16 @@
         <v>206</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3542,13 +3542,13 @@
         <v>206</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="D32" s="1" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3556,16 +3556,16 @@
         <v>206</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3573,16 +3573,16 @@
         <v>206</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3590,16 +3590,16 @@
         <v>206</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3607,16 +3607,16 @@
         <v>206</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3624,16 +3624,16 @@
         <v>206</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C37" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3641,16 +3641,16 @@
         <v>206</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>111</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3658,16 +3658,16 @@
         <v>206</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>111</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3675,16 +3675,16 @@
         <v>206</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3692,16 +3692,16 @@
         <v>206</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3709,16 +3709,16 @@
         <v>206</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C42" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="E42" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3726,16 +3726,16 @@
         <v>206</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3743,16 +3743,16 @@
         <v>206</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>302</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3760,13 +3760,13 @@
         <v>206</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="D45" s="1" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3774,13 +3774,13 @@
         <v>206</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3788,13 +3788,13 @@
         <v>206</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="D47" s="1" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3802,16 +3802,16 @@
         <v>206</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C48" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3819,13 +3819,13 @@
         <v>206</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>29</v>
@@ -3836,16 +3836,16 @@
         <v>206</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3853,16 +3853,16 @@
         <v>206</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C51" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="E51" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3870,16 +3870,16 @@
         <v>206</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="E52" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3887,16 +3887,16 @@
         <v>206</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C53" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="E53" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3904,16 +3904,16 @@
         <v>206</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C54" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="E54" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3921,16 +3921,16 @@
         <v>206</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C55" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -3966,35 +3966,35 @@
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>173</v>
@@ -4008,13 +4008,13 @@
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>173</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>90</v>
@@ -4022,179 +4022,179 @@
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>173</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>348</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>351</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>353</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>26</v>
@@ -4202,19 +4202,19 @@
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4254,95 +4254,95 @@
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>90</v>
@@ -4350,41 +4350,41 @@
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>90</v>
@@ -4392,27 +4392,27 @@
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>26</v>
@@ -4423,67 +4423,67 @@
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="1048576" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4521,10 +4521,10 @@
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>52</v>
@@ -4538,10 +4538,10 @@
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>49</v>
@@ -4555,55 +4555,55 @@
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>111</v>
@@ -4611,44 +4611,44 @@
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>408</v>
+        <v>449</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>409</v>
+        <v>450</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>411</v>
-      </c>
       <c r="D9" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>90</v>
@@ -4656,27 +4656,27 @@
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>425</v>
+        <v>451</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
@@ -4688,37 +4688,37 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>422</v>
-      </c>
       <c r="E14" s="3" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="F14" s="2"/>
     </row>

--- a/SurveyQuestions/csvs/hms_survey.xlsx
+++ b/SurveyQuestions/csvs/hms_survey.xlsx
@@ -993,7 +993,7 @@
     <t xml:space="preserve">Displayed if "No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
   </si>
   <si>
-    <t xml:space="preserve">Which of the following are important reasons why you received those services? (Select all that apply)</t>
+    <t xml:space="preserve">Which of the following are important reasons why you received the counselling services? (Select all that apply)</t>
   </si>
   <si>
     <t xml:space="preserve">1=I decided on my own to seek help. 2=A friend encouraged me to seek help. 3=A friend pressured me to seek help. 4=A family member encouraged me to seek help. 5=A family member pressured me to seek help. 6=Someone other than a friend or family member encouraged me to seek help  7= A campus advisor mandated me to seek help 11= A campus advisor referred me to seek help 8=I acquired more information about my options from  10= A health professional recommended or referred me to seek help. 12=Others</t>
@@ -1486,19 +1486,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1756,694 +1756,694 @@
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E19" s="0" t="s">
+      <c r="E19" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E21" s="0" t="s">
+      <c r="E21" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E25" s="0" t="s">
+      <c r="E25" s="1" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E26" s="0" t="s">
+      <c r="E26" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C27" s="0" t="s">
+      <c r="C27" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E27" s="0" t="s">
+      <c r="E27" s="1" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="C28" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="1" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E30" s="0" t="s">
+      <c r="E30" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E31" s="0" t="s">
+      <c r="E31" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E32" s="0" t="s">
+      <c r="E32" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E33" s="0" t="s">
+      <c r="E33" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D34" s="0" t="s">
+      <c r="D34" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E35" s="0" t="s">
+      <c r="E35" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C36" s="0" t="s">
+      <c r="C36" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E36" s="0" t="s">
+      <c r="E36" s="1" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C37" s="0" t="s">
+      <c r="C37" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E37" s="0" t="s">
+      <c r="E37" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C38" s="0" t="s">
+      <c r="C38" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D38" s="0" t="s">
+      <c r="D38" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E38" s="0" t="s">
+      <c r="E38" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C39" s="0" t="s">
+      <c r="C39" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="D39" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E39" s="0" t="s">
+      <c r="E39" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C40" s="0" t="s">
+      <c r="C40" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D40" s="0" t="s">
+      <c r="D40" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D41" s="0" t="s">
+      <c r="D41" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E41" s="0" t="s">
+      <c r="E41" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C42" s="0" t="s">
+      <c r="C42" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D42" s="0" t="s">
+      <c r="D42" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E42" s="0" t="s">
+      <c r="E42" s="1" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B43" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C43" s="0" t="s">
+      <c r="C43" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D43" s="0" t="s">
+      <c r="D43" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E43" s="0" t="s">
+      <c r="E43" s="1" t="s">
         <v>115</v>
       </c>
     </row>
@@ -2466,519 +2466,519 @@
   <dimension ref="A1:E1048576"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="1" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" s="1" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" s="1" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E19" s="0" t="s">
+      <c r="E19" s="1" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" s="1" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E21" s="0" t="s">
+      <c r="E21" s="1" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E22" s="0" t="s">
+      <c r="E22" s="1" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E24" s="0" t="s">
+      <c r="E24" s="1" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E25" s="0" t="s">
+      <c r="E25" s="1" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E26" s="0" t="s">
+      <c r="E26" s="1" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C27" s="0" t="s">
+      <c r="C27" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E27" s="0" t="s">
+      <c r="E27" s="1" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="C28" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E28" s="0" t="s">
+      <c r="E28" s="1" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="1" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="E30" s="0" t="s">
+      <c r="E30" s="1" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E31" s="0" t="s">
+      <c r="E31" s="1" t="s">
         <v>206</v>
       </c>
     </row>
@@ -3011,918 +3011,918 @@
   <dimension ref="A1:E55"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="52.31"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B2" s="0" t="s">
+      <c r="A2" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="A3" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B4" s="0" t="s">
+      <c r="A4" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B5" s="0" t="s">
+      <c r="A5" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B6" s="0" t="s">
+      <c r="A6" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B7" s="0" t="s">
+      <c r="A7" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B8" s="0" t="s">
+      <c r="A8" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B9" s="0" t="s">
+      <c r="A9" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B10" s="0" t="s">
+      <c r="A10" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B11" s="0" t="s">
+      <c r="A11" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B12" s="0" t="s">
+      <c r="A12" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B13" s="0" t="s">
+      <c r="A13" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B14" s="0" t="s">
+      <c r="A14" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B15" s="0" t="s">
+      <c r="A15" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="1" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B16" s="0" t="s">
+      <c r="A16" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" s="1" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B17" s="0" t="s">
+      <c r="A17" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" s="1" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B18" s="0" t="s">
+      <c r="A18" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" s="1" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B19" s="0" t="s">
+      <c r="A19" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E19" s="0" t="s">
+      <c r="E19" s="1" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B20" s="0" t="s">
+      <c r="A20" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B21" s="0" t="s">
+      <c r="A21" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E21" s="0" t="s">
+      <c r="E21" s="1" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B22" s="0" t="s">
+      <c r="A22" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B23" s="0" t="s">
+      <c r="A23" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="E23" s="0" t="s">
+      <c r="E23" s="1" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B24" s="0" t="s">
+      <c r="A24" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="E24" s="0" t="s">
+      <c r="E24" s="1" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B25" s="0" t="s">
+      <c r="A25" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="0" t="s">
+      <c r="E25" s="1" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B26" s="0" t="s">
+      <c r="A26" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="E26" s="0" t="s">
+      <c r="E26" s="1" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B27" s="0" t="s">
+      <c r="A27" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C27" s="0" t="s">
+      <c r="C27" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="E27" s="0" t="s">
+      <c r="E27" s="1" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B28" s="0" t="s">
+      <c r="A28" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="C28" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E28" s="0" t="s">
+      <c r="E28" s="1" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B29" s="0" t="s">
+      <c r="A29" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E29" s="0" t="s">
+      <c r="E29" s="1" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B30" s="0" t="s">
+      <c r="A30" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E30" s="0" t="s">
+      <c r="E30" s="1" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B31" s="0" t="s">
+      <c r="A31" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="E31" s="0" t="s">
+      <c r="E31" s="1" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B32" s="0" t="s">
+      <c r="A32" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="1" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B33" s="0" t="s">
+      <c r="A33" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="E33" s="0" t="s">
+      <c r="E33" s="1" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B34" s="0" t="s">
+      <c r="A34" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="D34" s="0" t="s">
+      <c r="D34" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="E34" s="0" t="s">
+      <c r="E34" s="1" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B35" s="0" t="s">
+      <c r="A35" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="E35" s="0" t="s">
+      <c r="E35" s="1" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B36" s="0" t="s">
+      <c r="A36" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C36" s="0" t="s">
+      <c r="C36" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="E36" s="0" t="s">
+      <c r="E36" s="1" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B37" s="0" t="s">
+      <c r="A37" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C37" s="0" t="s">
+      <c r="C37" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E37" s="0" t="s">
+      <c r="E37" s="1" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B38" s="0" t="s">
+      <c r="A38" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C38" s="0" t="s">
+      <c r="C38" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="D38" s="0" t="s">
+      <c r="D38" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E38" s="0" t="s">
+      <c r="E38" s="1" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B39" s="0" t="s">
+      <c r="A39" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C39" s="0" t="s">
+      <c r="C39" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="D39" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E39" s="0" t="s">
+      <c r="E39" s="1" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B40" s="0" t="s">
+      <c r="A40" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C40" s="0" t="s">
+      <c r="C40" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="D40" s="0" t="s">
+      <c r="D40" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="E40" s="0" t="s">
+      <c r="E40" s="1" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B41" s="0" t="s">
+      <c r="A41" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="D41" s="0" t="s">
+      <c r="D41" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="E41" s="0" t="s">
+      <c r="E41" s="1" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B42" s="0" t="s">
+      <c r="A42" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C42" s="0" t="s">
+      <c r="C42" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="D42" s="0" t="s">
+      <c r="D42" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="E42" s="0" t="s">
+      <c r="E42" s="1" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B43" s="0" t="s">
+      <c r="A43" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C43" s="0" t="s">
+      <c r="C43" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="D43" s="0" t="s">
+      <c r="D43" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="E43" s="0" t="s">
+      <c r="E43" s="1" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B44" s="0" t="s">
+      <c r="A44" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C44" s="0" t="s">
+      <c r="C44" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="D44" s="0" t="s">
+      <c r="D44" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="E44" s="0" t="s">
+      <c r="E44" s="1" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B45" s="0" t="s">
+      <c r="A45" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="C45" s="0" t="s">
+      <c r="C45" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="D45" s="0" t="s">
+      <c r="D45" s="1" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B46" s="0" t="s">
+      <c r="A46" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="C46" s="0" t="s">
+      <c r="C46" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="D46" s="0" t="s">
+      <c r="D46" s="1" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B47" s="0" t="s">
+      <c r="A47" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="C47" s="0" t="s">
+      <c r="C47" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="D47" s="0" t="s">
+      <c r="D47" s="1" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B48" s="0" t="s">
+      <c r="A48" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="C48" s="0" t="s">
+      <c r="C48" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="D48" s="0" t="s">
+      <c r="D48" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="E48" s="0" t="s">
+      <c r="E48" s="1" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B49" s="0" t="s">
+      <c r="A49" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="C49" s="0" t="s">
+      <c r="C49" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="D49" s="0" t="s">
+      <c r="D49" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="E49" s="0" t="s">
+      <c r="E49" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B50" s="0" t="s">
+      <c r="A50" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="C50" s="0" t="s">
+      <c r="C50" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="D50" s="0" t="s">
+      <c r="D50" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E50" s="0" t="s">
+      <c r="E50" s="1" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B51" s="0" t="s">
+      <c r="A51" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="C51" s="0" t="s">
+      <c r="C51" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="D51" s="0" t="s">
+      <c r="D51" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="E51" s="0" t="s">
+      <c r="E51" s="1" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B52" s="0" t="s">
+      <c r="A52" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C52" s="0" t="s">
+      <c r="C52" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="D52" s="0" t="s">
+      <c r="D52" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="E52" s="0" t="s">
+      <c r="E52" s="1" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B53" s="0" t="s">
+      <c r="A53" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C53" s="0" t="s">
+      <c r="C53" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="D53" s="0" t="s">
+      <c r="D53" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="E53" s="0" t="s">
+      <c r="E53" s="1" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B54" s="0" t="s">
+      <c r="A54" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C54" s="0" t="s">
+      <c r="C54" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="D54" s="0" t="s">
+      <c r="D54" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="E54" s="0" t="s">
+      <c r="E54" s="1" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="B55" s="0" t="s">
+      <c r="A55" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C55" s="0" t="s">
+      <c r="C55" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="D55" s="0" t="s">
+      <c r="D55" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="E55" s="0" t="s">
+      <c r="E55" s="1" t="s">
         <v>352</v>
       </c>
     </row>
@@ -3945,274 +3945,274 @@
   <dimension ref="A1:E24"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="1" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" s="1" t="s">
         <v>387</v>
       </c>
     </row>
@@ -4243,253 +4243,253 @@
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" s="1" t="s">
         <v>428</v>
       </c>
     </row>
@@ -4513,229 +4513,229 @@
   <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="71.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="71.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="3"/>
+      <c r="F12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="F13" s="3"/>
+      <c r="F13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>448</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="F14" s="3"/>
+      <c r="F14" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/SurveyQuestions/csvs/hms_survey.xlsx
+++ b/SurveyQuestions/csvs/hms_survey.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Demographics" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="455">
   <si>
     <t xml:space="preserve">Module</t>
   </si>
@@ -1320,9 +1320,6 @@
   </si>
   <si>
     <t xml:space="preserve">Financial Stress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Socioeconom ic status</t>
   </si>
   <si>
     <t xml:space="preserve">Within the past 12 months I worried whether our food would run out before we got money to buy more.</t>
@@ -4539,7 +4536,7 @@
         <v>429</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>430</v>
+        <v>48</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>52</v>
@@ -4556,7 +4553,7 @@
         <v>429</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>430</v>
+        <v>48</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>49</v>
@@ -4573,13 +4570,13 @@
         <v>429</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4587,13 +4584,13 @@
         <v>429</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>430</v>
+        <v>48</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4601,13 +4598,13 @@
         <v>429</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>430</v>
+        <v>48</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>434</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4615,10 +4612,10 @@
         <v>429</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>437</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>111</v>
@@ -4629,16 +4626,16 @@
         <v>429</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4646,13 +4643,13 @@
         <v>429</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4660,10 +4657,10 @@
         <v>429</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>444</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>90</v>
@@ -4674,13 +4671,13 @@
         <v>429</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4688,10 +4685,10 @@
         <v>429</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>448</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>449</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
@@ -4706,16 +4703,16 @@
         <v>429</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>451</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>452</v>
       </c>
       <c r="F13" s="1"/>
     </row>
@@ -4724,16 +4721,16 @@
         <v>429</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>454</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>455</v>
       </c>
       <c r="F14" s="1"/>
     </row>

--- a/SurveyQuestions/csvs/hms_survey.xlsx
+++ b/SurveyQuestions/csvs/hms_survey.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Demographics" sheetId="1" state="visible" r:id="rId3"/>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">1=Strong negative effect 2=Somewhat negative effect 3=No effect/neutral effect 4=Somewhat positive effect 5=Strong positive effect</t>
   </si>
   <si>
-    <t xml:space="preserve">Display if selected “6=PhD (or equivalent doctoral program” as degree program.</t>
+    <t xml:space="preserve">Display if "MS by Research scholar" or "PhD Scholar" is selected for "What is your role at IIITB?" (Faculty Advising is a PhD/research-degree program dependency -- references the Demographics Role question, not a question in this module.</t>
   </si>
   <si>
     <t xml:space="preserve">Overall social experience</t>
@@ -4238,6 +4238,11 @@
   </sheetPr>
   <dimension ref="A1:E1048576"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="36.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24.76"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">

--- a/SurveyQuestions/csvs/hms_survey.xlsx
+++ b/SurveyQuestions/csvs/hms_survey.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Demographics" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="453">
   <si>
     <t xml:space="preserve">Module</t>
   </si>
@@ -471,9 +471,6 @@
     <t xml:space="preserve">Please answer the following yes/no questions: Do you ever hear the voice of someone talking that other people cannot hear? Have you ever felt that someone was playing with your mind?</t>
   </si>
   <si>
-    <t xml:space="preserve">0=No 1=Yes</t>
-  </si>
-  <si>
     <t xml:space="preserve">Matrix table with 2 questions. Two-item screen for early psychosis (Phalen, et al., 2018)</t>
   </si>
   <si>
@@ -915,7 +912,7 @@
     <t xml:space="preserve">In the past 12 months have you taken any of the following types of prescription medications? (Please count only those you took, or are taking, several times per week.) (Select all that apply)</t>
   </si>
   <si>
-    <t xml:space="preserve">1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Others  8=No, none of these [mutually exclusive] 9=Don’t know</t>
+    <t xml:space="preserve">1=Psychostimulants (methylphenidate, amphetamine salts), dextroamphetamine, etc.) 2=Antidepressants (e.g., fluoxetin,sertraline,paroxetine,escitalopra,venlafaxine,bupropion, etc.) 3=Antipsychotics (e.g., haloperidol,clozapine,risperidone,olanzapine,etc.) 4=Anti-anxiety medications (e.g., lorazepam,clonazepam,alprazolam,buspirone,etc.) 5=Mood stabilizers (e.g., lithium, valproate,lamotrigine,carbamazepine,etc.) 6=Sleep medications (e.g., zolpidem,zaleplon,etc.) 7=Others  8=No, none of these [mutually exclusive] 9=Don’t know</t>
   </si>
   <si>
     <t xml:space="preserve">For what reason(s) do you use Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) ? (Select all that apply)</t>
@@ -951,9 +948,6 @@
     <t xml:space="preserve">Of the medication(s) you just noted, which are you currently taking? (Select all that apply)</t>
   </si>
   <si>
-    <t xml:space="preserve">1=Psychostimulants (methylphenidate (Ritalin, or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Other medication for mental or emotional health  8=None of the above [mutually exclusive]</t>
-  </si>
-  <si>
     <t xml:space="preserve">Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?" Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
   </si>
   <si>
@@ -1218,7 +1212,7 @@
     <t xml:space="preserve">Matrix table with 3 questions.</t>
   </si>
   <si>
-    <t xml:space="preserve">How frequently do instructors in your major/field of study grade your work on a curve (adjust grades based on the grade distribution among students in a class)?</t>
+    <t xml:space="preserve">How often do professors or external examiners in your course/department use relative grading (scaling or adjusting marks based on the overall performance of the class rather than using fixed passing marks)? </t>
   </si>
   <si>
     <t xml:space="preserve">1=Never 2=Almost never 3=Occasionally/sometimes 4=Almost every time 5=Every time</t>
@@ -1268,7 +1262,7 @@
     <t xml:space="preserve">How much do you agree with the following statements? I have doubts about whether higher education is worth the time, money, and effort that I’m spending on it. My family is very supportive of my educational goals. My professors believe in my potential to succeed academically.</t>
   </si>
   <si>
-    <t xml:space="preserve">How has it been to adjust to the academic demands of [college/graduate school] since you began as a student at your school?</t>
+    <t xml:space="preserve">How has it been to adjust to the academic demands of college since you began as a student at your school?</t>
   </si>
   <si>
     <t xml:space="preserve">1=Very easy 2=Easy 3=Somewhat easy 4=Somewhat difficult 5=Difficult 6=Very difficult</t>
@@ -1478,12 +1472,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2645,10 +2643,10 @@
         <v>147</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2656,16 +2654,16 @@
         <v>118</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2673,10 +2671,10 @@
         <v>118</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>111</v>
@@ -2687,16 +2685,16 @@
         <v>118</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2704,16 +2702,16 @@
         <v>118</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2721,10 +2719,10 @@
         <v>118</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>26</v>
@@ -2735,16 +2733,16 @@
         <v>118</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2752,16 +2750,16 @@
         <v>118</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2769,16 +2767,16 @@
         <v>118</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2786,16 +2784,16 @@
         <v>118</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2803,16 +2801,16 @@
         <v>118</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2820,16 +2818,16 @@
         <v>118</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2837,13 +2835,13 @@
         <v>118</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2851,16 +2849,16 @@
         <v>118</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2868,16 +2866,16 @@
         <v>118</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="E25" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2885,16 +2883,16 @@
         <v>118</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="E26" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2902,16 +2900,16 @@
         <v>118</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="E27" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2919,16 +2917,16 @@
         <v>118</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="E28" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2936,13 +2934,13 @@
         <v>118</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2950,16 +2948,16 @@
         <v>118</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2967,16 +2965,16 @@
         <v>118</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="1048567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3031,313 +3029,313 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C3" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C4" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C5" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C6" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C7" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C8" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C9" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C10" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C11" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C12" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>256</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>90</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>259</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>90</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>262</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>90</v>
@@ -3345,477 +3343,477 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>90</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>303</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C36" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="E36" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C37" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>111</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>111</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>29</v>
@@ -3823,104 +3821,104 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C51" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="E52" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C53" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C55" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -3964,55 +3962,55 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>90</v>
@@ -4020,177 +4018,177 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>361</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>26</v>
@@ -4198,19 +4196,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4239,9 +4237,9 @@
   <dimension ref="A1:E1048576"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="36.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="31.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="36.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="24.76"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4263,95 +4261,95 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>90</v>
@@ -4359,41 +4357,41 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>407</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>90</v>
@@ -4401,98 +4399,101 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4538,7 +4539,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>48</v>
@@ -4550,12 +4551,12 @@
         <v>50</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>48</v>
@@ -4567,60 +4568,60 @@
         <v>50</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>111</v>
@@ -4628,44 +4629,44 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>90</v>
@@ -4673,69 +4674,69 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="D12" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="4" t="s">
         <v>29</v>
       </c>
       <c r="F12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="B13" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>449</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>451</v>
       </c>
       <c r="F13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="C14" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>452</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>454</v>
       </c>
       <c r="F14" s="1"/>
     </row>

--- a/SurveyQuestions/csvs/hms_survey.xlsx
+++ b/SurveyQuestions/csvs/hms_survey.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Demographics" sheetId="1" state="visible" r:id="rId3"/>
@@ -1346,13 +1346,13 @@
     <t xml:space="preserve">Display if “Yes” is selected for “Do you have any concerns about your current living situation, like housing conditions, safety, and costs?”</t>
   </si>
   <si>
+    <t xml:space="preserve">Financing education</t>
+  </si>
+  <si>
     <t xml:space="preserve">Which of the following have you used to pay for educational expenses (room, board, tuition, and fees)? (Select all that apply)</t>
   </si>
   <si>
     <t xml:space="preserve">1=Family resources (parents, relatives, spouse, etc.) 2=Your own resources (income from work, work-study, etc.) 3=Aid that need not be repaid (grants, scholarships, military, etc.) 4=Aid that must be repaid (loans) 5=Other sources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Financing education</t>
   </si>
   <si>
     <t xml:space="preserve">To what extent do you agree or disagree with the following statements? I am worried about my ability to pay for school. I am worried about my ability to repay my student loans in the future [if loans selected above] My student loans negatively impact my mental health [if loans selected above]</t>
@@ -4475,7 +4475,7 @@
       <c r="D15" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="2" t="s">
         <v>156</v>
       </c>
     </row>
@@ -4649,13 +4649,13 @@
         <v>427</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4663,7 +4663,7 @@
         <v>427</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>441</v>

--- a/SurveyQuestions/csvs/hms_survey.xlsx
+++ b/SurveyQuestions/csvs/hms_survey.xlsx
@@ -4556,6 +4556,11 @@
           <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Somewhat disagree 5=Disagree 6=Strongly disagree</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Matrix table with 3 statements.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="6">
       <c r="A11" s="7" t="inlineStr">
@@ -4974,7 +4979,7 @@
           <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Somewhat disagree 5=Disagree 6=Strongly disagree</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Matrix table with 3 statements.</t>
         </is>

--- a/SurveyQuestions/csvs/hms_survey.xlsx
+++ b/SurveyQuestions/csvs/hms_survey.xlsx
@@ -888,7 +888,7 @@
     <t xml:space="preserve">Display only if “Have you ever received counseling or therapy for mental health concerns?” is not “No, Never.”</t>
   </si>
   <si>
-    <t xml:space="preserve">How satisfied/dissatisfied are you with the following aspects of your therapy or counseling that you received in the past 12 months at [pipe in selected options from: “From which of the following places did you receive counseling or therapy?”]? Convenient hours Location [Do not display for digital resources] Quality of therapists/counselors Respect for my privacy concerns Ability to schedule appointments without long delays Respect and consideration for my identities (e.g., race/ethnicity, gender, etc.)</t>
+    <t xml:space="preserve">How satisfied/dissatisfied are you with the following aspects of your therapy or counseling that you received in the past 12 months at [pipe in selected options from: “From which of the following places did you receive counseling or therapy?”]? Convenient hours Location [Do not display for digital resources] Quality of therapists/counselors Respect for my privacy concerns Ability to schedule appointments without long delays Respect and consideration for my beliefs (e.g., faith, gender, etc.)</t>
   </si>
   <si>
     <t xml:space="preserve">Display only if "Have you ever received counseling or therapy for mental health concerns?" is not "No, Never." One matrix table question with 6 statements for each option selected for "From which of the following places did you receive counseling or therapy?" (Up to 8)</t>
@@ -1483,19 +1483,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4398,7 +4398,7 @@
       <c r="D10" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>411</v>
       </c>
     </row>

--- a/SurveyQuestions/csvs/hms_survey.xlsx
+++ b/SurveyQuestions/csvs/hms_survey.xlsx
@@ -993,7 +993,7 @@
     <t xml:space="preserve">Which of the following are important reasons why you received those services? (Select all that apply)</t>
   </si>
   <si>
-    <t xml:space="preserve">1=I decided on my own to seek help. 2=A friend encouraged me to seek help. 3=A friend pressured me to seek help. 4=A family member encouraged me to seek help. 5=A family member pressured me to seek help. 6=Someone other than a friend or family member encouraged me to seek help  7= A campus advisor mandated me to seek help 11= A campus advisor referred me to seek help 8=I acquired more information about my options from  10= A health professional recommended or referred me to seek help. 12=Others</t>
+    <t xml:space="preserve">1=I decided on my own to seek help. 2=A friend encouraged me to seek help. 3=A friend pressured me to seek help. 4=A family member encouraged me to seek help. 5=A family member pressured me to seek help. 6=Someone other than a friend or family member encouraged me to seek help  7= A campus advisor mandated me to seek help 11= A campus advisor referred me to seek help  10= A health professional recommended or referred me to seek help. 12=Others</t>
   </si>
   <si>
     <t xml:space="preserve">Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?" or "2=Yes, prior to starting at this school" is selected for "Have you ever received counseling or therapy for mental health concerns?" or "3=Yes, since starting at this school" is selected for "Have you ever received counseling or therapy for mental health concerns?" or "4=Yes, both of the above (prior to and since starting at this school)" is selected for "Have you ever received counseling or therapy for mental health concerns?"</t>

--- a/SurveyQuestions/csvs/hms_survey.xlsx
+++ b/SurveyQuestions/csvs/hms_survey.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="454">
   <si>
     <t xml:space="preserve">Module</t>
   </si>
@@ -454,9 +454,6 @@
   </si>
   <si>
     <t xml:space="preserve">Included if ‘Eating and Body Image’ module not selected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDE</t>
   </si>
   <si>
     <t xml:space="preserve">Please answer the following questions as honestly as possible.
@@ -1488,19 +1485,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2627,16 +2624,16 @@
         <v>118</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2644,16 +2641,16 @@
         <v>118</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2661,16 +2658,16 @@
         <v>118</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2678,10 +2675,10 @@
         <v>118</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>111</v>
@@ -2692,16 +2689,16 @@
         <v>118</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2709,16 +2706,16 @@
         <v>118</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2726,10 +2723,10 @@
         <v>118</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>26</v>
@@ -2740,16 +2737,16 @@
         <v>118</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2757,16 +2754,16 @@
         <v>118</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2774,16 +2771,16 @@
         <v>118</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2791,16 +2788,16 @@
         <v>118</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2808,16 +2805,16 @@
         <v>118</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2825,16 +2822,16 @@
         <v>118</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2842,13 +2839,13 @@
         <v>118</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2856,16 +2853,16 @@
         <v>118</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2873,16 +2870,16 @@
         <v>118</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="E25" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2890,16 +2887,16 @@
         <v>118</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="E26" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2907,16 +2904,16 @@
         <v>118</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="E27" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2924,16 +2921,16 @@
         <v>118</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="E28" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2941,13 +2938,13 @@
         <v>118</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2955,16 +2952,16 @@
         <v>118</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2972,16 +2969,16 @@
         <v>118</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="1048567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3036,313 +3033,313 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C3" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C4" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C5" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C6" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C7" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C8" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C9" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C10" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C11" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C12" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>256</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>90</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>259</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>90</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>262</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>90</v>
@@ -3350,477 +3347,477 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>90</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>303</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C36" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="E36" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C37" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>111</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>111</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C40" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="E40" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C42" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="E42" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="E44" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C46" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C48" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C49" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>335</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>29</v>
@@ -3828,104 +3825,104 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C51" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="E51" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="E52" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C53" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="E53" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C54" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="E54" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C55" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="E55" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -3969,55 +3966,55 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>90</v>
@@ -4025,177 +4022,177 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>361</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>375</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>26</v>
@@ -4203,19 +4200,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4268,95 +4265,95 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>405</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>90</v>
@@ -4364,146 +4361,146 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>90</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>412</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="D15" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>427</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4549,7 +4546,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>48</v>
@@ -4561,12 +4558,12 @@
         <v>50</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>48</v>
@@ -4578,60 +4575,60 @@
         <v>50</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>436</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>111</v>
@@ -4639,75 +4636,75 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>90</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>448</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
@@ -4719,37 +4716,37 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>450</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>451</v>
       </c>
       <c r="F13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>453</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>454</v>
       </c>
       <c r="F14" s="1"/>
     </row>

--- a/SurveyQuestions/csvs/hms_survey.xlsx
+++ b/SurveyQuestions/csvs/hms_survey.xlsx
@@ -605,7 +605,7 @@
     <t xml:space="preserve">In which venues was the death by suicide discussed or acknowledged? Select all that apply.</t>
   </si>
   <si>
-    <t xml:space="preserve">1=An official institutional communication (e.g., email, emergency alert system) 2=A memorial 3=News media (e.g., newspapers or blogs) 4=Social media (e.g., Reddit, Instagram, Meta, X) 5=Word of mouth from my peers 6=Others  7=I don’t remember [mutually exclusive] 8=None of these</t>
+    <t xml:space="preserve">1=An official institutional communication (e.g., email, emergency alert system) 2=A memorial 3=News media (e.g., newspapers or blogs) 4=Social media (e.g., Reddit, Instagram, Meta, X) 5=Word of mouth from my peers 6=Others  7=I don’t remember [mutually exclusive] 8=None of these [mutually exclusive]</t>
   </si>
   <si>
     <t xml:space="preserve">Thinking about the effect of the person’s suicide on your life, what response is closest to your experience?</t>
